--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/OHIO_2016.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/OHIO_2016.xlsx
@@ -1842,7 +1842,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C83">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C117">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C210">
@@ -4243,7 +4243,7 @@
         <v>47</v>
       </c>
       <c r="D216">
-        <v>0.009652906140891353</v>
+        <v>0.009652906140891352</v>
       </c>
     </row>
     <row r="217">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec -Distrito 08-</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C539">
@@ -10464,7 +10464,7 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C562">
